--- a/sns-team-training/②SNS運用理解_マニュアル.xlsx
+++ b/sns-team-training/②SNS運用理解_マニュアル.xlsx
@@ -526,7 +526,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>対象：新メンバー ／ 中心アカウント：メイン(@libetee_travel)・カタログ ／ 主戦場：Instagram・TikTok</t>
+          <t>対象：新メンバー ／ 運用3アカウント：travel(メイン)・official(サブ)・japan(写真用) ／ 主戦場：Instagram・TikTok</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Q1. メインとカタログの役割・KPIの違いを説明できる？</t>
+          <t>Q1. travel/official/japan の3アカウントの役割の違いを説明できる？</t>
         </is>
       </c>
     </row>
@@ -565,10 +565,10 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="42" customHeight="1">
+    <row r="10" ht="48" customHeight="1">
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>各アカウントの役割とKPIを区別し、フィード/リール/ストーリーを目的別に使い分けられる状態。合図＝『この投稿はどのアカウントに・どの形式で出す？』に理由付きで即答できる。</t>
+          <t>3アカウント(travel/official/japan)の役割とKPIを区別し、フィード/リール/ストーリーを目的別に使い分けられる状態。合図＝『この投稿はどのアカウントに・どの形式で出す？』に理由付きで即答できる。</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
     <row r="13" ht="36" customHeight="1">
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>アカウントと投稿形式には役割がある。ここを外すと『認知したいのに商品ゴリ押し』等の的外れが起きる。制作(④)・投稿(⑥)・分析(⑦)全ての前提。</t>
+          <t>アカウントと投稿形式には役割がある。ここを外すと『認知用の写真アカウントに商品ゴリ押し』等の的外れが起きる。制作(④)・投稿(⑥)・分析(⑦)全ての前提。</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
     <row r="25" ht="24" customHeight="1">
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>4. 手順①：アカウントの役割を整理（Libetee）</t>
+          <t>4. 手順①：3アカウントの役割を整理（Libetee）</t>
         </is>
       </c>
     </row>
@@ -753,15 +753,15 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="34" customHeight="1">
+    <row r="27" ht="40" customHeight="1">
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>メイン(@libetee_travel)</t>
+          <t>メイン @libetee_travel</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>ブランド認知・集客。リール中心</t>
+          <t>ブランド認知・集客の主軸。旅行/出張の使用シーン。リール中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -770,37 +770,37 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="34" customHeight="1">
+    <row r="28" ht="40" customHeight="1">
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>カタログ</t>
+          <t>サブ @libetee_official</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>商品紹介・訴求。フィードで商品を並べる</t>
+          <t>公式情報・商品訴求・実績/レビュー/キャンペーン発信</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>プロフ遷移率／楽天への送客</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
+          <t>プロフ遷移率／楽天送客／保存</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1">
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>(補足)ハンディファン/ドライヤー</t>
+          <t>写真用 @libetee_japan</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>同じ考え方で応用。今回は割愛</t>
+          <t>ビジュアル・世界観づくり。高品質写真でブランドイメージ</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>プロフィール到達／ブランド想起(定性)</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>パッキング術／開封／機能実演で発見タブ狙い</t>
+          <t>パッキング術／開封／機能実演で発見タブ狙い(主にtravel)</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>スペック比較／実績(楽天1位)／カラー一覧</t>
+          <t>スペック比較／実績/カラー一覧(official)・世界観写真(japan)</t>
         </is>
       </c>
     </row>
@@ -910,14 +910,14 @@
     <row r="42" ht="24" customHeight="1">
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>4. 手順④：自社アカウントを観察（30分）</t>
+          <t>4. 手順④：3アカウントを観察（各15分）</t>
         </is>
       </c>
     </row>
     <row r="43" ht="42" customHeight="1">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>@libetee_travel を開き、直近20投稿を『形式・テーマ・伸びた投稿』で分類しメモ。伸びている型を3つ書き出す。※IG現状(フォロワー/bio)は要確認。</t>
+          <t>travel/official/japan を順に開き、各アカウントの『発信テーマ・形式・伸びた投稿』を分類しメモ。3アカウントの違いを1行ずつ言語化する。※各bio/フォロワーは要確認。</t>
         </is>
       </c>
     </row>
@@ -928,17 +928,17 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="30" customHeight="1">
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>・目的とKPIを対応させる：認知=リーチ/保存、集客=プロフ遷移、売上=送客</t>
+          <t>・アカウントの役割を混ぜない：travel=認知/使用シーン、official=商品/実績、japan=世界観写真</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>・形式の役割を守る：リールで新規獲得、フィードで信頼、ストーリーで接触</t>
+          <t>・目的とKPIを対応：認知=リーチ/保存、集客=プロフ遷移、売上=送客</t>
         </is>
       </c>
     </row>
@@ -973,24 +973,24 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="34" customHeight="1">
+    <row r="52" ht="38" customHeight="1">
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>形式選択</t>
+          <t>アカウント選択</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>新機能の紹介を静止画フィードだけで投稿</t>
+          <t>世界観重視のjapanに機能スペックをびっしり投稿</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>リールで機能実演→保存を狙い、フィードにも要点を残す</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="34" customHeight="1">
+          <t>スペック/実績はofficial、japanは高品質な使用シーン写真で世界観</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
       <c r="B53" s="5" t="inlineStr">
         <is>
           <t>指標の見方</t>
@@ -1031,7 +1031,7 @@
     <row r="58">
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>□ メインとカタログの役割・KPIを区別できる</t>
+          <t>□ travel/official/japanの役割とKPIを区別できる</t>
         </is>
       </c>
     </row>
@@ -1059,14 +1059,14 @@
     <row r="62">
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>□ @libetee_travelの伸びている投稿の型を3つ挙げた</t>
+          <t>□ 3アカウントの伸びている投稿の型を各1つ以上挙げた</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>□ 『この投稿はどこに・どの形式で』を理由付きで判断できる</t>
+          <t>□ 『この投稿はどのアカウントに・どの形式で』を理由付きで判断できる</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
     <row r="66">
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>1. 企画を『アカウント×形式×KPI』で振り分けられる</t>
+          <t>1. 企画を『アカウント(travel/official/japan)×形式×KPI』で振り分けられる</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
     <row r="68">
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>3. 自社アカウントの伸びる型を自分の言葉で説明できる</t>
+          <t>3. 3アカウントの役割の違いを自分の言葉で説明できる</t>
         </is>
       </c>
     </row>
@@ -1108,14 +1108,14 @@
     <row r="71">
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>・各アカウントのKPIと合格ライン数値（保存率○%等）は？</t>
+          <t>・各アカウント(travel/official/japan)のKPIと合格ライン数値は？</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>・投稿形式の配分（リール週○本 等）の現状は？</t>
+          <t>・3アカウントの投稿頻度・形式配分の現状は？</t>
         </is>
       </c>
     </row>
@@ -1129,14 +1129,14 @@
     <row r="74">
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>・TikTokは運用する？頻度は？</t>
+          <t>・TikTokは運用する？どのアカウント連動？</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>・カタログの送客先は楽天でOK？計測方法は？</t>
+          <t>・official→楽天への送客の計測方法は？</t>
         </is>
       </c>
     </row>

--- a/sns-team-training/②SNS運用理解_マニュアル.xlsx
+++ b/sns-team-training/②SNS運用理解_マニュアル.xlsx
@@ -526,7 +526,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>対象：新メンバー ／ 運用3アカウント：travel(メイン)・official(サブ)・japan(写真用) ／ 主戦場：Instagram・TikTok</t>
+          <t>対象：新メンバー ／ 運用3アカウント：travel(メイン)・official(予備)・japan(一眼・世界観) ／ 主戦場：Instagram・TikTok</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
     <row r="13" ht="36" customHeight="1">
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>アカウントと投稿形式には役割がある。ここを外すと『認知用の写真アカウントに商品ゴリ押し』等の的外れが起きる。制作(④)・投稿(⑥)・分析(⑦)全ての前提。</t>
+          <t>アカウントごとに役割が違う。ここを外すと『世界観用のjapanにスペックびっしり』等の的外れが起きる。制作(④)・投稿(⑥)・分析(⑦)全ての前提。</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
     <row r="22">
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>発見タブ／おすすめ</t>
+          <t>凍結/BAN</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>未フォロワーに露出する面</t>
+          <t>規約違反等でアカウントが停止・削除されること</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>新規リーチの源泉</t>
+          <t>予備アカウントが必要な理由</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
     <row r="25" ht="24" customHeight="1">
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>4. 手順①：3アカウントの役割を整理（Libetee）</t>
+          <t>4. 手順①：3アカウントの役割を整理（Libetee 確定）</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="40" customHeight="1">
+    <row r="27" ht="48" customHeight="1">
       <c r="B27" s="5" t="inlineStr">
         <is>
           <t>メイン @libetee_travel</t>
@@ -761,7 +761,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>ブランド認知・集客の主軸。旅行/出張の使用シーン。リール中心</t>
+          <t>認知拡大（ブランド認知の主軸）。旅行/出張の使用シーンをリールで発信し新規リーチを最大化</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -770,24 +770,24 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="40" customHeight="1">
+    <row r="28" ht="48" customHeight="1">
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>サブ @libetee_official</t>
+          <t>予備 @libetee_official</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>公式情報・商品訴求・実績/レビュー/キャンペーン発信</t>
+          <t>バックアップ用。万一メインが凍結・削除された時の受け皿（リスク分散）。普段はメイン投稿を転載し稼働維持</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>プロフ遷移率／楽天送客／保存</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="40" customHeight="1">
+          <t>稼働維持／フォロワー確保(保険)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1">
       <c r="B29" s="5" t="inlineStr">
         <is>
           <t>写真用 @libetee_japan</t>
@@ -795,12 +795,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>ビジュアル・世界観づくり。高品質写真でブランドイメージ</t>
+          <t>一眼(ミラーレス/一眼レフ)で撮影した高品質画像でブランド感・世界観を高める</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>プロフィール到達／ブランド想起(定性)</t>
+          <t>ブランド想起(定性)／プロフィール到達</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>スペック比較／実績/カラー一覧(official)・世界観写真(japan)</t>
+          <t>travel=使用シーン/実績、japan=一眼の高品質ビジュアル</t>
         </is>
       </c>
     </row>
@@ -931,14 +931,14 @@
     <row r="46" ht="30" customHeight="1">
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>・アカウントの役割を混ぜない：travel=認知/使用シーン、official=商品/実績、japan=世界観写真</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
+          <t>・アカウントの役割を混ぜない：travel=認知拡大、official=予備(保険)、japan=一眼の世界観</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>・目的とKPIを対応：認知=リーチ/保存、集客=プロフ遷移、売上=送客</t>
+          <t>・officialはメインのリスク分散が目的。主要投稿を転載して常に稼働状態にしておく</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="38" customHeight="1">
+    <row r="52" ht="42" customHeight="1">
       <c r="B52" s="5" t="inlineStr">
         <is>
           <t>アカウント選択</t>
@@ -981,29 +981,29 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>世界観重視のjapanに機能スペックをびっしり投稿</t>
+          <t>一眼で世界観を出すjapanに機能スペックをびっしり投稿</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>スペック/実績はofficial、japanは高品質な使用シーン写真で世界観</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="30" customHeight="1">
+          <t>スペック/機能はtravelのリール、japanは一眼の高品質ビジュアルでブランド感</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="42" customHeight="1">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>指標の見方</t>
+          <t>予備の放置</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>いいね数だけで良し悪しを判断</t>
+          <t>officialを作ったまま放置し、メイン凍結時に受け皿が育っていない</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>保存率・視聴維持率・プロフ遷移で評価する</t>
+          <t>officialにメイン投稿を定期転載し、いざという時の受け皿を維持</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
     <row r="58">
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>□ travel/official/japanの役割とKPIを区別できる</t>
+          <t>□ travel=認知/official=予備/japan=一眼世界観 の役割を区別できる</t>
         </is>
       </c>
     </row>
@@ -1052,14 +1052,14 @@
     <row r="61">
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>□ 目的(認知/集客/売上)とKPIを対応づけられる</t>
+          <t>□ officialが必要な理由(凍結リスク分散)を説明できる</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>□ 3アカウントの伸びている投稿の型を各1つ以上挙げた</t>
+          <t>□ 3アカウントの伸びている/発信の型を各1つ以上挙げた</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
     <row r="68">
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>3. 3アカウントの役割の違いを自分の言葉で説明できる</t>
+          <t>3. 3アカウントの役割の違い(認知/予備/一眼世界観)を自分の言葉で説明できる</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
     <row r="72">
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>・3アカウントの投稿頻度・形式配分の現状は？</t>
+          <t>・officialへの転載ルール・頻度は決まっている？</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
     <row r="75">
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>・official→楽天への送客の計測方法は？</t>
+          <t>・japanの一眼撮影の担当・機材は？</t>
         </is>
       </c>
     </row>
